--- a/data/trans_camb/P1418-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1418-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,01</t>
+          <t>1,51</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,89</t>
+          <t>1,27</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,74; -0,52</t>
+          <t>-5,78; -0,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,37; -2,35</t>
+          <t>-7,47; -2,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 4,28</t>
+          <t>-2,77; 3,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 3,75</t>
+          <t>-2,51; 3,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 0,33</t>
+          <t>-5,82; 0,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 4,86</t>
+          <t>-1,6; 4,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 0,99</t>
+          <t>-2,87; 1,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,89; -1,53</t>
+          <t>-5,72; -1,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 4,31</t>
+          <t>-0,84; 3,34</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-45,93; -5,41</t>
+          <t>-46,68; -7,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-59,36; -23,12</t>
+          <t>-59,22; -23,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,63; 42,7</t>
+          <t>-22,69; 33,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,56; 23,06</t>
+          <t>-12,64; 23,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,81; 2,07</t>
+          <t>-29,83; 4,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 29,14</t>
+          <t>-8,48; 28,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-18,44; 7,0</t>
+          <t>-18,3; 8,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,63; -10,77</t>
+          <t>-35,39; -10,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 30,65</t>
+          <t>-5,32; 24,22</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,15</t>
+          <t>0,17</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,07</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>0,44</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; -0,85</t>
+          <t>-2,78; -0,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,54; -0,51</t>
+          <t>-2,57; -0,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,9</t>
+          <t>-1,01; 1,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 1,16</t>
+          <t>-2,01; 1,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 0,45</t>
+          <t>-2,6; 0,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 1,52</t>
+          <t>-0,77; 1,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,07; -0,23</t>
+          <t>-2,13; -0,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,16; -0,4</t>
+          <t>-2,19; -0,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,87</t>
+          <t>-0,51; 1,33</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-5,02%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-1,23%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-1,98%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-75,54; -28,73</t>
+          <t>-75,67; -28,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-68,63; -18,8</t>
+          <t>-69,15; -20,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-40,12; 38,16</t>
+          <t>-27,6; 52,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,04; 24,32</t>
+          <t>-31,71; 31,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,17; 10,69</t>
+          <t>-40,54; 11,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,96; 31,03</t>
+          <t>-11,66; 45,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-44,31; -6,01</t>
+          <t>-44,48; -7,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,06; -11,36</t>
+          <t>-46,32; -9,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-26,26; 22,89</t>
+          <t>-11,01; 36,71</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,81</t>
+          <t>-0,91</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,07</t>
+          <t>-0,05</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 0,28</t>
+          <t>-3,19; 0,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,52; -0,42</t>
+          <t>-3,62; -0,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 0,69</t>
+          <t>-2,83; 0,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 0,13</t>
+          <t>-4,64; -0,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 0,69</t>
+          <t>-3,98; 0,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 2,91</t>
+          <t>-1,69; 2,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,36; -0,52</t>
+          <t>-3,11; -0,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,06; -0,26</t>
+          <t>-3,13; -0,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 1,36</t>
+          <t>-1,56; 1,28</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-32,05%</t>
+          <t>-36,2%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-2,28%</t>
+          <t>-1,61%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-92,02; 47,83</t>
+          <t>-89,09; 49,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 2,23</t>
+          <t>-93,66; 4,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-71,35; 53,17</t>
+          <t>-73,15; 43,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-78,61; 14,88</t>
+          <t>-83,55; 1,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-73,49; 30,08</t>
+          <t>-72,25; 46,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-34,57; 117,06</t>
+          <t>-30,86; 109,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-77,04; -14,11</t>
+          <t>-76,56; -9,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-74,58; -9,32</t>
+          <t>-75,49; -9,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-39,75; 56,11</t>
+          <t>-36,42; 56,71</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,46</t>
+          <t>-1,25</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,89</t>
+          <t>-1,35</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,65</t>
+          <t>-1,27</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,24; -1,32</t>
+          <t>-3,32; -1,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,93; -2,09</t>
+          <t>-3,9; -2,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,69; -0,41</t>
+          <t>-2,26; -0,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 1,16</t>
+          <t>-2,01; 1,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,45; -1,71</t>
+          <t>-4,57; -1,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,66; -0,39</t>
+          <t>-2,77; -0,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,28; -0,48</t>
+          <t>-2,3; -0,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,86; -2,14</t>
+          <t>-3,93; -2,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,77; -0,77</t>
+          <t>-2,05; -0,39</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-26,68%</t>
+          <t>-22,95%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-18,59%</t>
+          <t>-13,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-21,02%</t>
+          <t>-16,22%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-54,71; -27,98</t>
+          <t>-55,23; -26,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-66,27; -42,77</t>
+          <t>-65,95; -41,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-44,73; -8,62</t>
+          <t>-37,25; -4,99</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,35; 12,07</t>
+          <t>-17,89; 10,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-40,41; -18,1</t>
+          <t>-40,92; -16,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-33,71; -4,24</t>
+          <t>-24,98; -1,99</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-26,64; -6,53</t>
+          <t>-27,68; -6,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-46,43; -28,72</t>
+          <t>-46,94; -29,01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-33,94; -10,61</t>
+          <t>-24,97; -5,43</t>
         </is>
       </c>
     </row>
